--- a/output/report2.xlsx
+++ b/output/report2.xlsx
@@ -442,11 +442,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -591,115 +591,257 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cutoff Date</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
+          <t>Total Leads</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>224</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fallback Price</t>
+          <t>Paid Leads</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8999</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
+          <t>Unpaid Leads</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Raw Meta Spend</t>
+          <t>Paid Funnel %</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>87.94642857142857</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Attributed Meta Spend</t>
+          <t>Unpaid Funnel %</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>12.05357142857143</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unallocated Meta Spend</t>
+          <t>Attributed Leads</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Total Sales</t>
+          <t>Unattributed Leads</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Attributed Sales</t>
+          <t>Total Sales</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Unattributed Sales</t>
+          <t>Attributed Sales</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total Revenue</t>
+          <t>Unattributed Sales</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>62993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Per Sale Value</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>6990</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Attributed Per Sale Value</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>6990</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Registration Amount</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sales Revenue</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>48930</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Registration Revenue</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>48930</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Attributed Revenue</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>53994</v>
+      <c r="B29" t="n">
+        <v>41940</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unattributed Revenue</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>6990</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Raw Meta Spend</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Attributed Spend</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unallocated Spend</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Profit</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>41940</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ROAS</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ROI</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CAC</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -713,7 +855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV1"/>
+  <dimension ref="A1:CU1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -727,7 +869,7 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="17" customWidth="1" min="15" max="15"/>
@@ -795,27 +937,26 @@
     <col width="11" customWidth="1" min="77" max="77"/>
     <col width="18" customWidth="1" min="78" max="78"/>
     <col width="9" customWidth="1" min="79" max="79"/>
-    <col width="14" customWidth="1" min="80" max="80"/>
-    <col width="15" customWidth="1" min="81" max="81"/>
-    <col width="23" customWidth="1" min="82" max="82"/>
-    <col width="10" customWidth="1" min="83" max="83"/>
-    <col width="8" customWidth="1" min="84" max="84"/>
-    <col width="13" customWidth="1" min="85" max="85"/>
-    <col width="20" customWidth="1" min="86" max="86"/>
-    <col width="13" customWidth="1" min="87" max="87"/>
-    <col width="11" customWidth="1" min="88" max="88"/>
-    <col width="12" customWidth="1" min="89" max="89"/>
-    <col width="9" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
-    <col width="21" customWidth="1" min="92" max="92"/>
-    <col width="19" customWidth="1" min="93" max="93"/>
-    <col width="14" customWidth="1" min="94" max="94"/>
-    <col width="18" customWidth="1" min="95" max="95"/>
-    <col width="14" customWidth="1" min="96" max="96"/>
-    <col width="20" customWidth="1" min="97" max="97"/>
-    <col width="26" customWidth="1" min="98" max="98"/>
-    <col width="15" customWidth="1" min="99" max="99"/>
-    <col width="22" customWidth="1" min="100" max="100"/>
+    <col width="15" customWidth="1" min="80" max="80"/>
+    <col width="23" customWidth="1" min="81" max="81"/>
+    <col width="10" customWidth="1" min="82" max="82"/>
+    <col width="8" customWidth="1" min="83" max="83"/>
+    <col width="13" customWidth="1" min="84" max="84"/>
+    <col width="20" customWidth="1" min="85" max="85"/>
+    <col width="13" customWidth="1" min="86" max="86"/>
+    <col width="11" customWidth="1" min="87" max="87"/>
+    <col width="12" customWidth="1" min="88" max="88"/>
+    <col width="9" customWidth="1" min="89" max="89"/>
+    <col width="18" customWidth="1" min="90" max="90"/>
+    <col width="21" customWidth="1" min="91" max="91"/>
+    <col width="19" customWidth="1" min="92" max="92"/>
+    <col width="14" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
+    <col width="14" customWidth="1" min="95" max="95"/>
+    <col width="20" customWidth="1" min="96" max="96"/>
+    <col width="26" customWidth="1" min="97" max="97"/>
+    <col width="15" customWidth="1" min="98" max="98"/>
+    <col width="22" customWidth="1" min="99" max="99"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -876,7 +1017,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Amount Received (Sub)</t>
+          <t>order_amount</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1216,105 +1357,100 @@
       </c>
       <c r="CB1" s="1" t="inlineStr">
         <is>
-          <t>order_amount</t>
+          <t>amount_source</t>
         </is>
       </c>
       <c r="CC1" s="1" t="inlineStr">
         <is>
-          <t>amount_source</t>
+          <t>payment_status_source</t>
         </is>
       </c>
       <c r="CD1" s="1" t="inlineStr">
         <is>
-          <t>payment_status_source</t>
+          <t>campaign</t>
         </is>
       </c>
       <c r="CE1" s="1" t="inlineStr">
         <is>
-          <t>campaign</t>
+          <t>ad_set</t>
         </is>
       </c>
       <c r="CF1" s="1" t="inlineStr">
         <is>
-          <t>ad_set</t>
+          <t>ad_creative</t>
         </is>
       </c>
       <c r="CG1" s="1" t="inlineStr">
         <is>
-          <t>ad_creative</t>
+          <t>attribution_source</t>
         </is>
       </c>
       <c r="CH1" s="1" t="inlineStr">
         <is>
-          <t>attribution_source</t>
+          <t>match_level</t>
         </is>
       </c>
       <c r="CI1" s="1" t="inlineStr">
         <is>
-          <t>match_level</t>
+          <t>camp_norm</t>
         </is>
       </c>
       <c r="CJ1" s="1" t="inlineStr">
         <is>
-          <t>camp_norm</t>
+          <t>adset_norm</t>
         </is>
       </c>
       <c r="CK1" s="1" t="inlineStr">
         <is>
-          <t>adset_norm</t>
+          <t>ad_norm</t>
         </is>
       </c>
       <c r="CL1" s="1" t="inlineStr">
         <is>
-          <t>ad_norm</t>
+          <t>attributed_spend</t>
         </is>
       </c>
       <c r="CM1" s="1" t="inlineStr">
         <is>
-          <t>attributed_spend</t>
+          <t>registration_date_y</t>
         </is>
       </c>
       <c r="CN1" s="1" t="inlineStr">
         <is>
-          <t>registration_date_y</t>
+          <t>registration_date</t>
         </is>
       </c>
       <c r="CO1" s="1" t="inlineStr">
         <is>
-          <t>registration_date</t>
+          <t>webinar_type</t>
         </is>
       </c>
       <c r="CP1" s="1" t="inlineStr">
         <is>
-          <t>webinar_type</t>
+          <t>registration_fee</t>
         </is>
       </c>
       <c r="CQ1" s="1" t="inlineStr">
         <is>
-          <t>registration_fee</t>
+          <t>new_old_lead</t>
         </is>
       </c>
       <c r="CR1" s="1" t="inlineStr">
         <is>
-          <t>new_old_lead</t>
+          <t>webinar_type_clean</t>
         </is>
       </c>
       <c r="CS1" s="1" t="inlineStr">
         <is>
-          <t>webinar_type_clean</t>
+          <t>registration_fee_applied</t>
         </is>
       </c>
       <c r="CT1" s="1" t="inlineStr">
         <is>
-          <t>registration_fee_applied</t>
+          <t>total_revenue</t>
         </is>
       </c>
       <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>total_revenue</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>data_quality_warning</t>
         </is>
@@ -1331,7 +1467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1357,6 +1493,7 @@
     <col width="25" customWidth="1" min="21" max="21"/>
     <col width="19" customWidth="1" min="22" max="22"/>
     <col width="29" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1473,6 +1610,11 @@
       <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Results (initial) indicator</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>source_file_id</t>
         </is>
       </c>
     </row>
@@ -1596,11 +1738,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>62993</v>
+        <v>48930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C:62993.0, AS:62993.0, AD:62993.0</t>
+          <t>C:48930.0, AS:48930.0, AD:48930.0</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1736,10 +1878,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>143</v>
+        <v>224</v>
       </c>
       <c r="D9" t="n">
-        <v>143</v>
+        <v>224</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1836,17 +1978,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1891,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE35"/>
+  <dimension ref="A1:CD35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1905,7 +2047,7 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="17" customWidth="1" min="15" max="15"/>
@@ -1973,10 +2115,9 @@
     <col width="21" customWidth="1" min="77" max="77"/>
     <col width="18" customWidth="1" min="78" max="78"/>
     <col width="9" customWidth="1" min="79" max="79"/>
-    <col width="14" customWidth="1" min="80" max="80"/>
-    <col width="16" customWidth="1" min="81" max="81"/>
-    <col width="23" customWidth="1" min="82" max="82"/>
-    <col width="26" customWidth="1" min="83" max="83"/>
+    <col width="15" customWidth="1" min="80" max="80"/>
+    <col width="23" customWidth="1" min="81" max="81"/>
+    <col width="26" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2037,7 +2178,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Amount Received (Sub)</t>
+          <t>order_amount</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -2377,20 +2518,15 @@
       </c>
       <c r="CB1" s="1" t="inlineStr">
         <is>
-          <t>order_amount</t>
+          <t>amount_source</t>
         </is>
       </c>
       <c r="CC1" s="1" t="inlineStr">
         <is>
-          <t>amount_source</t>
+          <t>payment_status_source</t>
         </is>
       </c>
       <c r="CD1" s="1" t="inlineStr">
-        <is>
-          <t>payment_status_source</t>
-        </is>
-      </c>
-      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>exclusion_reason</t>
         </is>
@@ -2407,8 +2543,10 @@
           <t>pratibha3226@gmail.com</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>9360302396</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>9360302396</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2677,20 +2815,17 @@
       <c r="CA2" t="n">
         <v>1</v>
       </c>
-      <c r="CB2" s="2" t="n">
-        <v>8999</v>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -2707,8 +2842,10 @@
           <t>deepthi.darshan@gmail.com</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>9480516146</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>9480516146</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2977,20 +3114,17 @@
       <c r="CA3" t="n">
         <v>2</v>
       </c>
-      <c r="CB3" s="2" t="n">
-        <v>8999</v>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -3007,8 +3141,10 @@
           <t>drshailjapande@gmail.com</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>9891494973</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>9891494973</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3277,20 +3413,17 @@
       <c r="CA4" t="n">
         <v>3</v>
       </c>
-      <c r="CB4" s="2" t="n">
-        <v>8999</v>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -3307,8 +3440,10 @@
           <t>logeshwari.cloud@gmail.com</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>8748866501</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>8748866501</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3577,20 +3712,17 @@
       <c r="CA5" t="n">
         <v>4</v>
       </c>
-      <c r="CB5" s="2" t="n">
-        <v>8999</v>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -3607,8 +3739,10 @@
           <t>niyatif@gmail.com</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>8899202416</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>8899202416</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3877,20 +4011,17 @@
       <c r="CA6" t="n">
         <v>5</v>
       </c>
-      <c r="CB6" s="2" t="n">
-        <v>8999</v>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -3907,8 +4038,10 @@
           <t>kiran_puthran@hotmail.com</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>9619191127</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>9619191127</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4177,20 +4310,17 @@
       <c r="CA7" t="n">
         <v>6</v>
       </c>
-      <c r="CB7" s="2" t="n">
-        <v>8999</v>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -4207,8 +4337,10 @@
           <t>arpipatel1@gmail.com</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>9033036061</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>9033036061</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4477,20 +4609,17 @@
       <c r="CA8" t="n">
         <v>7</v>
       </c>
-      <c r="CB8" s="2" t="n">
-        <v>8999</v>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -4507,8 +4636,10 @@
           <t>priyankavpatil8@gmail.com</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>9049835216</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>9049835216</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4777,20 +4908,17 @@
       <c r="CA9" t="n">
         <v>8</v>
       </c>
-      <c r="CB9" s="2" t="n">
-        <v>8999</v>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -4807,8 +4935,10 @@
           <t>joycerosy.jr@gmail.com</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>9916260796</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>9916260796</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -5077,20 +5207,17 @@
       <c r="CA10" t="n">
         <v>9</v>
       </c>
-      <c r="CB10" s="2" t="n">
-        <v>8999</v>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -5107,8 +5234,10 @@
           <t>salvi.mayura1976@gmail.com</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>9923330110</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>9923330110</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5377,20 +5506,17 @@
       <c r="CA11" t="n">
         <v>10</v>
       </c>
-      <c r="CB11" s="2" t="n">
-        <v>8999</v>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -5407,8 +5533,10 @@
           <t>mailtoshree07@gmail.com</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>9538558933</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>9538558933</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5677,20 +5805,17 @@
       <c r="CA12" t="n">
         <v>11</v>
       </c>
-      <c r="CB12" s="2" t="n">
-        <v>8999</v>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -5707,8 +5832,10 @@
           <t>vaibhavi2006@gmail.com</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>9689531850</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>9689531850</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5977,20 +6104,17 @@
       <c r="CA13" t="n">
         <v>12</v>
       </c>
-      <c r="CB13" s="2" t="n">
-        <v>8999</v>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -6007,8 +6131,10 @@
           <t>pritikajohri@gmail.com</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>9962210323</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>9962210323</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6277,20 +6403,17 @@
       <c r="CA14" t="n">
         <v>13</v>
       </c>
-      <c r="CB14" s="2" t="n">
-        <v>8999</v>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE14" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -6307,8 +6430,10 @@
           <t>chillampallymanisha@gmail.com</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>9059370850</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>9059370850</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6577,20 +6702,17 @@
       <c r="CA15" t="n">
         <v>14</v>
       </c>
-      <c r="CB15" s="2" t="n">
-        <v>8999</v>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -6607,8 +6729,10 @@
           <t>kudtarkar.archana.25@gmail.com</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>8291210037</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>8291210037</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -6877,20 +7001,17 @@
       <c r="CA16" t="n">
         <v>15</v>
       </c>
-      <c r="CB16" s="2" t="n">
-        <v>8999</v>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE16" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -6907,8 +7028,10 @@
           <t>yvumadevi@gmail.com</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>8446610535</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>8446610535</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -7177,20 +7300,17 @@
       <c r="CA17" t="n">
         <v>16</v>
       </c>
-      <c r="CB17" s="2" t="n">
-        <v>8999</v>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE17" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -7207,8 +7327,10 @@
           <t>singhla.aashvi5@gmail.com</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>8699236275</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>8699236275</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -7477,20 +7599,17 @@
       <c r="CA18" t="n">
         <v>17</v>
       </c>
-      <c r="CB18" s="2" t="n">
-        <v>8999</v>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE18" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -7507,8 +7626,10 @@
           <t>anitabose@gmail.com</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>9873197747</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>9873197747</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -7777,20 +7898,17 @@
       <c r="CA19" t="n">
         <v>18</v>
       </c>
-      <c r="CB19" s="2" t="n">
-        <v>8999</v>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE19" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -7807,8 +7925,10 @@
           <t>jelsia293@gmail.com</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>7708592813</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>7708592813</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -8077,20 +8197,17 @@
       <c r="CA20" t="n">
         <v>19</v>
       </c>
-      <c r="CB20" s="2" t="n">
-        <v>8999</v>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE20" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -8107,8 +8224,10 @@
           <t>vkhamborkar@gmail.com</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>8793211595</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>8793211595</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -8377,20 +8496,17 @@
       <c r="CA21" t="n">
         <v>20</v>
       </c>
-      <c r="CB21" s="2" t="n">
-        <v>8999</v>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE21" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -8407,8 +8523,10 @@
           <t>dr.knisha@gmail.com</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>9731574492</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>9731574492</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -8677,20 +8795,17 @@
       <c r="CA22" t="n">
         <v>21</v>
       </c>
-      <c r="CB22" s="2" t="n">
-        <v>8999</v>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE22" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -8707,8 +8822,10 @@
           <t>mohinit1190@gmail.com</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>9167639490</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>9167639490</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -8982,20 +9099,17 @@
       <c r="CA23" t="n">
         <v>29</v>
       </c>
-      <c r="CB23" s="2" t="n">
-        <v>8999</v>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE23" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -9012,8 +9126,10 @@
           <t>nivedhaharibabu@gmail.com</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>9791063154</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>9791063154</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -9282,20 +9398,17 @@
       <c r="CA24" t="n">
         <v>30</v>
       </c>
-      <c r="CB24" s="2" t="n">
-        <v>8999</v>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC24" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD24" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE24" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -9312,8 +9425,10 @@
           <t>puipath10@gmail.com</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>9845673844</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>9845673844</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -9582,20 +9697,17 @@
       <c r="CA25" t="n">
         <v>31</v>
       </c>
-      <c r="CB25" s="2" t="n">
-        <v>8999</v>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC25" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD25" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE25" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -9612,8 +9724,10 @@
           <t>neelam.1903@gmail.com</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>9911703398</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>9911703398</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -9882,20 +9996,17 @@
       <c r="CA26" t="n">
         <v>32</v>
       </c>
-      <c r="CB26" s="2" t="n">
-        <v>8999</v>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC26" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD26" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE26" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -9912,8 +10023,10 @@
           <t>bhagvatichoudhary03@gmail.com</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>9673313650</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>9673313650</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -10182,20 +10295,17 @@
       <c r="CA27" t="n">
         <v>33</v>
       </c>
-      <c r="CB27" s="2" t="n">
-        <v>8999</v>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC27" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD27" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE27" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -10212,8 +10322,10 @@
           <t>ksgscse@gmail.com</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>9444702450</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>9444702450</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -10482,20 +10594,17 @@
       <c r="CA28" t="n">
         <v>34</v>
       </c>
-      <c r="CB28" s="2" t="n">
-        <v>8999</v>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC28" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD28" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE28" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -10512,8 +10621,10 @@
           <t>sakshipahwa2018@gmail.com</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>9910744885</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>9910744885</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -10782,20 +10893,17 @@
       <c r="CA29" t="n">
         <v>35</v>
       </c>
-      <c r="CB29" s="2" t="n">
-        <v>8999</v>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC29" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD29" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE29" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -10812,8 +10920,10 @@
           <t>k11.rashmi@gmail.com</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>7406703335</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>7406703335</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -11082,20 +11192,17 @@
       <c r="CA30" t="n">
         <v>36</v>
       </c>
-      <c r="CB30" s="2" t="n">
-        <v>8999</v>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC30" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD30" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE30" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -11112,8 +11219,10 @@
           <t>latha.kn1811@gmail.com</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>9538175099</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>9538175099</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -11382,20 +11491,17 @@
       <c r="CA31" t="n">
         <v>37</v>
       </c>
-      <c r="CB31" s="2" t="n">
-        <v>8999</v>
+      <c r="CB31" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC31" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD31" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE31" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -11412,8 +11518,10 @@
           <t>nehaconnect123@gmail.com</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>9769223732</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>9769223732</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -11682,20 +11790,17 @@
       <c r="CA32" t="n">
         <v>38</v>
       </c>
-      <c r="CB32" s="2" t="n">
-        <v>8999</v>
+      <c r="CB32" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC32" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD32" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE32" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -11712,8 +11817,10 @@
           <t>nelsonsharon22@yahoo.com</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>7356597993</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>7356597993</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -11982,20 +12089,17 @@
       <c r="CA33" t="n">
         <v>39</v>
       </c>
-      <c r="CB33" s="2" t="n">
-        <v>8999</v>
+      <c r="CB33" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC33" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD33" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE33" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -12012,8 +12116,10 @@
           <t>pillutllahimabindu@gmail.com</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>8121749890</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>8121749890</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -12282,20 +12388,17 @@
       <c r="CA34" t="n">
         <v>40</v>
       </c>
-      <c r="CB34" s="2" t="n">
-        <v>8999</v>
+      <c r="CB34" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC34" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD34" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE34" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -12312,8 +12415,10 @@
           <t>reachdelphine@gmail.com</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>9916725925</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>9916725925</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -12582,20 +12687,17 @@
       <c r="CA35" t="n">
         <v>41</v>
       </c>
-      <c r="CB35" s="2" t="n">
-        <v>8999</v>
+      <c r="CB35" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC35" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD35" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="CE35" t="inlineStr">
         <is>
           <t>Outside Reporting Period</t>
         </is>
@@ -12612,7 +12714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV8"/>
+  <dimension ref="A1:CU8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12626,7 +12728,7 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="17" customWidth="1" min="15" max="15"/>
@@ -12694,27 +12796,26 @@
     <col width="21" customWidth="1" min="77" max="77"/>
     <col width="18" customWidth="1" min="78" max="78"/>
     <col width="9" customWidth="1" min="79" max="79"/>
-    <col width="14" customWidth="1" min="80" max="80"/>
-    <col width="16" customWidth="1" min="81" max="81"/>
-    <col width="23" customWidth="1" min="82" max="82"/>
-    <col width="50" customWidth="1" min="83" max="83"/>
-    <col width="28" customWidth="1" min="84" max="84"/>
-    <col width="50" customWidth="1" min="85" max="85"/>
-    <col width="20" customWidth="1" min="86" max="86"/>
-    <col width="14" customWidth="1" min="87" max="87"/>
-    <col width="50" customWidth="1" min="88" max="88"/>
-    <col width="28" customWidth="1" min="89" max="89"/>
-    <col width="50" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
-    <col width="21" customWidth="1" min="92" max="92"/>
-    <col width="19" customWidth="1" min="93" max="93"/>
-    <col width="14" customWidth="1" min="94" max="94"/>
-    <col width="18" customWidth="1" min="95" max="95"/>
-    <col width="14" customWidth="1" min="96" max="96"/>
-    <col width="20" customWidth="1" min="97" max="97"/>
-    <col width="26" customWidth="1" min="98" max="98"/>
-    <col width="15" customWidth="1" min="99" max="99"/>
-    <col width="23" customWidth="1" min="100" max="100"/>
+    <col width="15" customWidth="1" min="80" max="80"/>
+    <col width="23" customWidth="1" min="81" max="81"/>
+    <col width="50" customWidth="1" min="82" max="82"/>
+    <col width="28" customWidth="1" min="83" max="83"/>
+    <col width="50" customWidth="1" min="84" max="84"/>
+    <col width="20" customWidth="1" min="85" max="85"/>
+    <col width="14" customWidth="1" min="86" max="86"/>
+    <col width="50" customWidth="1" min="87" max="87"/>
+    <col width="28" customWidth="1" min="88" max="88"/>
+    <col width="50" customWidth="1" min="89" max="89"/>
+    <col width="18" customWidth="1" min="90" max="90"/>
+    <col width="21" customWidth="1" min="91" max="91"/>
+    <col width="19" customWidth="1" min="92" max="92"/>
+    <col width="14" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
+    <col width="14" customWidth="1" min="95" max="95"/>
+    <col width="20" customWidth="1" min="96" max="96"/>
+    <col width="26" customWidth="1" min="97" max="97"/>
+    <col width="15" customWidth="1" min="98" max="98"/>
+    <col width="22" customWidth="1" min="99" max="99"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12775,7 +12876,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Amount Received (Sub)</t>
+          <t>order_amount</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -13115,105 +13216,100 @@
       </c>
       <c r="CB1" s="1" t="inlineStr">
         <is>
-          <t>order_amount</t>
+          <t>amount_source</t>
         </is>
       </c>
       <c r="CC1" s="1" t="inlineStr">
         <is>
-          <t>amount_source</t>
+          <t>payment_status_source</t>
         </is>
       </c>
       <c r="CD1" s="1" t="inlineStr">
         <is>
-          <t>payment_status_source</t>
+          <t>campaign</t>
         </is>
       </c>
       <c r="CE1" s="1" t="inlineStr">
         <is>
-          <t>campaign</t>
+          <t>ad_set</t>
         </is>
       </c>
       <c r="CF1" s="1" t="inlineStr">
         <is>
-          <t>ad_set</t>
+          <t>ad_creative</t>
         </is>
       </c>
       <c r="CG1" s="1" t="inlineStr">
         <is>
-          <t>ad_creative</t>
+          <t>attribution_source</t>
         </is>
       </c>
       <c r="CH1" s="1" t="inlineStr">
         <is>
-          <t>attribution_source</t>
+          <t>match_level</t>
         </is>
       </c>
       <c r="CI1" s="1" t="inlineStr">
         <is>
-          <t>match_level</t>
+          <t>camp_norm</t>
         </is>
       </c>
       <c r="CJ1" s="1" t="inlineStr">
         <is>
-          <t>camp_norm</t>
+          <t>adset_norm</t>
         </is>
       </c>
       <c r="CK1" s="1" t="inlineStr">
         <is>
-          <t>adset_norm</t>
+          <t>ad_norm</t>
         </is>
       </c>
       <c r="CL1" s="1" t="inlineStr">
         <is>
-          <t>ad_norm</t>
+          <t>attributed_spend</t>
         </is>
       </c>
       <c r="CM1" s="1" t="inlineStr">
         <is>
-          <t>attributed_spend</t>
+          <t>registration_date_y</t>
         </is>
       </c>
       <c r="CN1" s="1" t="inlineStr">
         <is>
-          <t>registration_date_y</t>
+          <t>registration_date</t>
         </is>
       </c>
       <c r="CO1" s="1" t="inlineStr">
         <is>
-          <t>registration_date</t>
+          <t>webinar_type</t>
         </is>
       </c>
       <c r="CP1" s="1" t="inlineStr">
         <is>
-          <t>webinar_type</t>
+          <t>registration_fee</t>
         </is>
       </c>
       <c r="CQ1" s="1" t="inlineStr">
         <is>
-          <t>registration_fee</t>
+          <t>new_old_lead</t>
         </is>
       </c>
       <c r="CR1" s="1" t="inlineStr">
         <is>
-          <t>new_old_lead</t>
+          <t>webinar_type_clean</t>
         </is>
       </c>
       <c r="CS1" s="1" t="inlineStr">
         <is>
-          <t>webinar_type_clean</t>
+          <t>registration_fee_applied</t>
         </is>
       </c>
       <c r="CT1" s="1" t="inlineStr">
         <is>
-          <t>registration_fee_applied</t>
+          <t>total_revenue</t>
         </is>
       </c>
       <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>total_revenue</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>data_quality_warning</t>
         </is>
@@ -13230,8 +13326,10 @@
           <t>diarypreet@gmail.com</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>8951156002</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8951156002</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -13500,84 +13598,81 @@
       <c r="CA2" t="n">
         <v>22</v>
       </c>
-      <c r="CB2" s="2" t="n">
-        <v>8999</v>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>actual</t>
+          <t>ig</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>social</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>link_in_bio</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>Leads DB (email)</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>Ad Level</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
           <t>ig</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>social</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>link_in_bio</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
-        <is>
-          <t>Leads DB (email)</t>
-        </is>
-      </c>
-      <c r="CI2" t="inlineStr">
-        <is>
-          <t>Ad Level</t>
-        </is>
-      </c>
-      <c r="CJ2" t="inlineStr">
-        <is>
-          <t>ig</t>
-        </is>
-      </c>
-      <c r="CK2" t="inlineStr">
-        <is>
-          <t>social</t>
-        </is>
-      </c>
-      <c r="CL2" t="inlineStr">
-        <is>
-          <t>link_in_bio</t>
-        </is>
-      </c>
-      <c r="CM2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN2" s="4" t="n">
+      <c r="CL2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM2" s="4" t="n">
         <v>46239.38055555556</v>
       </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
           <t>none</t>
         </is>
       </c>
+      <c r="CS2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="CT2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU2" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>Fallback order_amount</t>
+        <v>6990</v>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>Actual Data</t>
         </is>
       </c>
     </row>
@@ -13592,8 +13687,10 @@
           <t>nikitavikas2018@gmail.com</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>9686622672</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>9686622672</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -13862,84 +13959,81 @@
       <c r="CA3" t="n">
         <v>23</v>
       </c>
-      <c r="CB3" s="2" t="n">
-        <v>8999</v>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>actual</t>
+          <t>Foremost Leads &lt;&gt; CBO &lt;&gt; Desk Format | Faceless</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>Foremost Leads &lt;&gt; CBO &lt;&gt; Desk Format | Faceless</t>
+          <t>Job Interests Women only</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>Job Interests Women only</t>
+          <t>If you're a women on Career Break Due to maternity  Due to marriage</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>If you're a women on Career Break Due to maternity  Due to marriage</t>
+          <t>Leads DB (email)</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>Leads DB (email)</t>
+          <t>Ad Level</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>Ad Level</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; desk format | faceless</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; desk format | faceless</t>
+          <t>job interests women only</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>job interests women only</t>
-        </is>
-      </c>
-      <c r="CL3" t="inlineStr">
-        <is>
           <t>if you're a women on career break due to maternity due to marriage</t>
         </is>
       </c>
-      <c r="CM3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN3" s="4" t="n">
+      <c r="CL3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM3" s="4" t="n">
         <v>46240.92083333333</v>
       </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
           <t>none</t>
         </is>
       </c>
+      <c r="CS3" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="CT3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU3" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="CV3" t="inlineStr">
-        <is>
-          <t>Fallback order_amount</t>
+        <v>6990</v>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>Actual Data</t>
         </is>
       </c>
     </row>
@@ -13954,8 +14048,10 @@
           <t>monicagosavi01@gmail.com</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>9769347947</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>9769347947</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -14224,84 +14320,81 @@
       <c r="CA4" t="n">
         <v>24</v>
       </c>
-      <c r="CB4" s="2" t="n">
-        <v>8999</v>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>actual</t>
+          <t>Foremost Leads &lt;&gt; CBO &lt;&gt; Image Ads | AI Generated</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>Foremost Leads &lt;&gt; CBO &lt;&gt; Image Ads | AI Generated</t>
+          <t>Housewives and Mothers</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>Housewives and Mothers</t>
+          <t>IMAGE AD | WhiteBoard | Iceberg | Women On Career Break</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>IMAGE AD | WhiteBoard | Iceberg | Women On Career Break</t>
+          <t>Leads DB (email)</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>Leads DB (email)</t>
+          <t>Ad Level</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>Ad Level</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; image ads | ai generated</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; image ads | ai generated</t>
+          <t>housewives and mothers</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>housewives and mothers</t>
-        </is>
-      </c>
-      <c r="CL4" t="inlineStr">
-        <is>
           <t>image ad | whiteboard | iceberg | women on career break</t>
         </is>
       </c>
-      <c r="CM4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN4" s="4" t="n">
+      <c r="CL4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM4" s="4" t="n">
         <v>46239.32569444444</v>
       </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
           <t>none</t>
         </is>
       </c>
+      <c r="CS4" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="CT4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU4" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="CV4" t="inlineStr">
-        <is>
-          <t>Fallback order_amount</t>
+        <v>6990</v>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>Actual Data</t>
         </is>
       </c>
     </row>
@@ -14316,8 +14409,10 @@
           <t>gunaswetha21@gmail.com</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>9148858262</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>9148858262</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -14586,84 +14681,81 @@
       <c r="CA5" t="n">
         <v>25</v>
       </c>
-      <c r="CB5" s="2" t="n">
-        <v>8999</v>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>actual</t>
+          <t>ig</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>social</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>link_in_bio</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>Leads DB (email)</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>Ad Level</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
           <t>ig</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>social</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>link_in_bio</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
-        <is>
-          <t>Leads DB (email)</t>
-        </is>
-      </c>
-      <c r="CI5" t="inlineStr">
-        <is>
-          <t>Ad Level</t>
-        </is>
-      </c>
-      <c r="CJ5" t="inlineStr">
-        <is>
-          <t>ig</t>
-        </is>
-      </c>
-      <c r="CK5" t="inlineStr">
-        <is>
-          <t>social</t>
-        </is>
-      </c>
-      <c r="CL5" t="inlineStr">
-        <is>
-          <t>link_in_bio</t>
-        </is>
-      </c>
-      <c r="CM5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN5" s="4" t="n">
+      <c r="CL5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" s="4" t="n">
         <v>46240.37222222222</v>
       </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="CS5" t="inlineStr">
-        <is>
           <t>none</t>
         </is>
       </c>
+      <c r="CS5" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="CT5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU5" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="CV5" t="inlineStr">
-        <is>
-          <t>Fallback order_amount</t>
+        <v>6990</v>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>Actual Data</t>
         </is>
       </c>
     </row>
@@ -14678,8 +14770,10 @@
           <t>manisharabade13@gmail.com</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>9403651740</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>9403651740</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -14948,84 +15042,81 @@
       <c r="CA6" t="n">
         <v>26</v>
       </c>
-      <c r="CB6" s="2" t="n">
-        <v>8999</v>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>actual</t>
+          <t>Foremost Leads &lt;&gt; CBO &lt;&gt; Master Campaign</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>Foremost Leads &lt;&gt; CBO &lt;&gt; Master Campaign</t>
+          <t>Housewives &amp; Moms – Copy</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>Housewives &amp; Moms – Copy</t>
+          <t>Confused about – Copy 2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>Confused about – Copy 2</t>
+          <t>Leads DB (email)</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>Leads DB (email)</t>
+          <t>Ad Level</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>Ad Level</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; master campaign</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; master campaign</t>
+          <t>housewives &amp; moms – copy</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>housewives &amp; moms – copy</t>
-        </is>
-      </c>
-      <c r="CL6" t="inlineStr">
-        <is>
           <t>confused about – copy 2</t>
         </is>
       </c>
-      <c r="CM6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN6" s="4" t="n">
+      <c r="CL6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" s="4" t="n">
         <v>46239.40069444444</v>
       </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="CS6" t="inlineStr">
-        <is>
           <t>none</t>
         </is>
       </c>
+      <c r="CS6" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="CT6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU6" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="CV6" t="inlineStr">
-        <is>
-          <t>Fallback order_amount</t>
+        <v>6990</v>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>Actual Data</t>
         </is>
       </c>
     </row>
@@ -15040,8 +15131,10 @@
           <t>minakshi283@gmail.com</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>8527655899</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8527655899</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -15310,55 +15403,52 @@
       <c r="CA7" t="n">
         <v>27</v>
       </c>
-      <c r="CB7" s="2" t="n">
-        <v>8999</v>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>fallback_price</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
           <t>actual</t>
         </is>
       </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>Unattributed</t>
+        </is>
+      </c>
       <c r="CH7" t="inlineStr">
         <is>
           <t>Unattributed</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
-        <is>
-          <t>Unattributed</t>
-        </is>
-      </c>
+      <c r="CI7" t="inlineStr"/>
       <c r="CJ7" t="inlineStr"/>
       <c r="CK7" t="inlineStr"/>
-      <c r="CL7" t="inlineStr"/>
-      <c r="CM7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN7" s="4" t="n"/>
+      <c r="CL7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" s="4" t="n"/>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="CS7" t="inlineStr">
-        <is>
           <t>none</t>
         </is>
       </c>
+      <c r="CS7" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="CT7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU7" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="CV7" t="inlineStr">
-        <is>
-          <t>Fallback order_amount</t>
+        <v>6990</v>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
+          <t>Actual Data</t>
         </is>
       </c>
     </row>
@@ -15373,8 +15463,10 @@
           <t>mnsabharadwaj@gmail.com</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>9901801703</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>9901801703</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -15643,84 +15735,81 @@
       <c r="CA8" t="n">
         <v>28</v>
       </c>
-      <c r="CB8" s="2" t="n">
-        <v>8999</v>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>fallback_price</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>actual</t>
+          <t>Foremost Leads &lt;&gt; ABO &lt;&gt; Master &lt;&gt; Scaled</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>Foremost Leads &lt;&gt; ABO &lt;&gt; Master &lt;&gt; Scaled</t>
+          <t>Housewives &amp; Moms – Copy 2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>Housewives &amp; Moms – Copy 2</t>
+          <t>Confused about – Copy 2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>Confused about – Copy 2</t>
+          <t>Leads DB (email)</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>Leads DB (email)</t>
+          <t>Ad Level</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>Ad Level</t>
+          <t>foremost leads &lt;&gt; abo &lt;&gt; master &lt;&gt; scaled</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; abo &lt;&gt; master &lt;&gt; scaled</t>
+          <t>housewives &amp; moms – copy 2</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>housewives &amp; moms – copy 2</t>
-        </is>
-      </c>
-      <c r="CL8" t="inlineStr">
-        <is>
           <t>confused about – copy 2</t>
         </is>
       </c>
-      <c r="CM8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN8" s="4" t="n">
+      <c r="CL8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" s="4" t="n">
         <v>46241.45138888889</v>
       </c>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="CS8" t="inlineStr">
-        <is>
           <t>none</t>
         </is>
       </c>
+      <c r="CS8" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="CT8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU8" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="CV8" t="inlineStr">
-        <is>
-          <t>Fallback order_amount</t>
+        <v>6990</v>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>Actual Data</t>
         </is>
       </c>
     </row>
@@ -15851,10 +15940,10 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>17998</v>
+        <v>13980</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>17998</v>
+        <v>13980</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -15904,10 +15993,10 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -15961,10 +16050,10 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -16018,10 +16107,10 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -16075,10 +16164,10 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -16132,10 +16221,10 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -16285,10 +16374,10 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -16342,10 +16431,10 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -16399,10 +16488,10 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -16456,10 +16545,10 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -16513,10 +16602,10 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -16570,10 +16659,10 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>17998</v>
+        <v>13980</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>17998</v>
+        <v>13980</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -16723,10 +16812,10 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -16780,10 +16869,10 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -16837,10 +16926,10 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -16894,10 +16983,10 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -16951,10 +17040,10 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>8999</v>
+        <v>6990</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -17008,10 +17097,10 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>17998</v>
+        <v>13980</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>17998</v>
+        <v>13980</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -17181,7 +17270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV2"/>
+  <dimension ref="A1:CU2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17195,7 +17284,7 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="17" customWidth="1" min="15" max="15"/>
@@ -17263,27 +17352,26 @@
     <col width="21" customWidth="1" min="77" max="77"/>
     <col width="18" customWidth="1" min="78" max="78"/>
     <col width="9" customWidth="1" min="79" max="79"/>
-    <col width="14" customWidth="1" min="80" max="80"/>
-    <col width="16" customWidth="1" min="81" max="81"/>
-    <col width="23" customWidth="1" min="82" max="82"/>
-    <col width="10" customWidth="1" min="83" max="83"/>
-    <col width="8" customWidth="1" min="84" max="84"/>
-    <col width="13" customWidth="1" min="85" max="85"/>
-    <col width="20" customWidth="1" min="86" max="86"/>
-    <col width="14" customWidth="1" min="87" max="87"/>
-    <col width="11" customWidth="1" min="88" max="88"/>
-    <col width="12" customWidth="1" min="89" max="89"/>
-    <col width="9" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
-    <col width="21" customWidth="1" min="92" max="92"/>
-    <col width="19" customWidth="1" min="93" max="93"/>
-    <col width="14" customWidth="1" min="94" max="94"/>
-    <col width="18" customWidth="1" min="95" max="95"/>
-    <col width="14" customWidth="1" min="96" max="96"/>
-    <col width="20" customWidth="1" min="97" max="97"/>
-    <col width="26" customWidth="1" min="98" max="98"/>
-    <col width="15" customWidth="1" min="99" max="99"/>
-    <col width="23" customWidth="1" min="100" max="100"/>
+    <col width="15" customWidth="1" min="80" max="80"/>
+    <col width="23" customWidth="1" min="81" max="81"/>
+    <col width="10" customWidth="1" min="82" max="82"/>
+    <col width="8" customWidth="1" min="83" max="83"/>
+    <col width="13" customWidth="1" min="84" max="84"/>
+    <col width="20" customWidth="1" min="85" max="85"/>
+    <col width="14" customWidth="1" min="86" max="86"/>
+    <col width="11" customWidth="1" min="87" max="87"/>
+    <col width="12" customWidth="1" min="88" max="88"/>
+    <col width="9" customWidth="1" min="89" max="89"/>
+    <col width="18" customWidth="1" min="90" max="90"/>
+    <col width="21" customWidth="1" min="91" max="91"/>
+    <col width="19" customWidth="1" min="92" max="92"/>
+    <col width="14" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
+    <col width="14" customWidth="1" min="95" max="95"/>
+    <col width="20" customWidth="1" min="96" max="96"/>
+    <col width="26" customWidth="1" min="97" max="97"/>
+    <col width="15" customWidth="1" min="98" max="98"/>
+    <col width="22" customWidth="1" min="99" max="99"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17344,7 +17432,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Amount Received (Sub)</t>
+          <t>order_amount</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -17684,105 +17772,100 @@
       </c>
       <c r="CB1" s="1" t="inlineStr">
         <is>
-          <t>order_amount</t>
+          <t>amount_source</t>
         </is>
       </c>
       <c r="CC1" s="1" t="inlineStr">
         <is>
-          <t>amount_source</t>
+          <t>payment_status_source</t>
         </is>
       </c>
       <c r="CD1" s="1" t="inlineStr">
         <is>
-          <t>payment_status_source</t>
+          <t>campaign</t>
         </is>
       </c>
       <c r="CE1" s="1" t="inlineStr">
         <is>
-          <t>campaign</t>
+          <t>ad_set</t>
         </is>
       </c>
       <c r="CF1" s="1" t="inlineStr">
         <is>
-          <t>ad_set</t>
+          <t>ad_creative</t>
         </is>
       </c>
       <c r="CG1" s="1" t="inlineStr">
         <is>
-          <t>ad_creative</t>
+          <t>attribution_source</t>
         </is>
       </c>
       <c r="CH1" s="1" t="inlineStr">
         <is>
-          <t>attribution_source</t>
+          <t>match_level</t>
         </is>
       </c>
       <c r="CI1" s="1" t="inlineStr">
         <is>
-          <t>match_level</t>
+          <t>camp_norm</t>
         </is>
       </c>
       <c r="CJ1" s="1" t="inlineStr">
         <is>
-          <t>camp_norm</t>
+          <t>adset_norm</t>
         </is>
       </c>
       <c r="CK1" s="1" t="inlineStr">
         <is>
-          <t>adset_norm</t>
+          <t>ad_norm</t>
         </is>
       </c>
       <c r="CL1" s="1" t="inlineStr">
         <is>
-          <t>ad_norm</t>
+          <t>attributed_spend</t>
         </is>
       </c>
       <c r="CM1" s="1" t="inlineStr">
         <is>
-          <t>attributed_spend</t>
+          <t>registration_date_y</t>
         </is>
       </c>
       <c r="CN1" s="1" t="inlineStr">
         <is>
-          <t>registration_date_y</t>
+          <t>registration_date</t>
         </is>
       </c>
       <c r="CO1" s="1" t="inlineStr">
         <is>
-          <t>registration_date</t>
+          <t>webinar_type</t>
         </is>
       </c>
       <c r="CP1" s="1" t="inlineStr">
         <is>
-          <t>webinar_type</t>
+          <t>registration_fee</t>
         </is>
       </c>
       <c r="CQ1" s="1" t="inlineStr">
         <is>
-          <t>registration_fee</t>
+          <t>new_old_lead</t>
         </is>
       </c>
       <c r="CR1" s="1" t="inlineStr">
         <is>
-          <t>new_old_lead</t>
+          <t>webinar_type_clean</t>
         </is>
       </c>
       <c r="CS1" s="1" t="inlineStr">
         <is>
-          <t>webinar_type_clean</t>
+          <t>registration_fee_applied</t>
         </is>
       </c>
       <c r="CT1" s="1" t="inlineStr">
         <is>
-          <t>registration_fee_applied</t>
+          <t>total_revenue</t>
         </is>
       </c>
       <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>total_revenue</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>data_quality_warning</t>
         </is>
@@ -17799,8 +17882,10 @@
           <t>minakshi283@gmail.com</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>8527655899</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8527655899</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -18069,55 +18154,52 @@
       <c r="CA2" t="n">
         <v>27</v>
       </c>
-      <c r="CB2" s="2" t="n">
-        <v>8999</v>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>fallback_price</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
           <t>actual</t>
         </is>
       </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>Unattributed</t>
+        </is>
+      </c>
       <c r="CH2" t="inlineStr">
         <is>
           <t>Unattributed</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
-        <is>
-          <t>Unattributed</t>
-        </is>
-      </c>
+      <c r="CI2" t="inlineStr"/>
       <c r="CJ2" t="inlineStr"/>
       <c r="CK2" t="inlineStr"/>
-      <c r="CL2" t="inlineStr"/>
-      <c r="CM2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN2" s="4" t="n"/>
+      <c r="CL2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM2" s="4" t="n"/>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
           <t>none</t>
         </is>
       </c>
+      <c r="CS2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="CT2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU2" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>Fallback order_amount</t>
+        <v>6990</v>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>Actual Data</t>
         </is>
       </c>
     </row>
